--- a/evidence/claim-verification.xlsx
+++ b/evidence/claim-verification.xlsx
@@ -1,23 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sanjayc/sebi-regulated-entity-accessibility/evidence/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC97CCF-1885-AB44-B0B2-1D7F7EB3626F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Claims" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Broker Data" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Charters" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Circulars" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Claims" sheetId="1" r:id="rId1"/>
+    <sheet name="Broker Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Charters" sheetId="3" r:id="rId3"/>
+    <sheet name="Circulars" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Claims!$A$1:$I$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Claims!$A$1:$I$49</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -28,1022 +44,1019 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="336">
   <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where it appears</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correction / note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supreme Court, 30 Apr 2025, held the right to digital access an intrinsic component of the right to life and personal liberty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article; guide Ch.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFIED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quoted verbatim inside the circular itself</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI 2025/111 Annexure I s.A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The case is Pragya Prasun &amp; Ors. v. Union of India, heard with a Jain matter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article; guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NARROWER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circular names 'Pragya Prasun &amp; Ors.' and 'Jain vs. Union of India'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First name 'Amar' comes from secondary coverage only. Article corrected to 'a Jain matter'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standards are WCAG 2.1 or latest, GIGW latest, IS 17802, RPwD Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article; guide Ch.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbatim, four numbered items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI 2025/111 Annexure I s.B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI never writes WCAG 2.2, GIGW 3.0, or a year for IS 17802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full text of four circulars searched</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111, 2025/121, 2025/131, Dec 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Nodal Officer for digital accessibility is mandatory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbatim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111 s.1.1-1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An accessibility-specific grievance mechanism with escalation is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111 s.1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investor PDFs must follow accessible document standards; circular cites the WCAG PDF techniques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbatim, with the W3C URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111 s.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISL, captions, descriptive audio and alt text are required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111 s.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audits must include usability testing by persons with disabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111 s.5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A disabled applicant may be rejected only after human review, with power to override automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111 s.4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsibility for platform accessibility stays with the RE even for SaaS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The circular says 'responsibility', not 'liability'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111 s.6.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article corrected: 'liability' replaced in two places.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audit and remediation deadline is 31 October 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circular reproduced inside an exchange notice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HO/(411)2026-ITD-5_DIV2/I/17922/2026 via BSE Notice 20260731-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 14 Dec 2025 auditor milestone was replaced, not supplemented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbatim: 'Instead of meeting the compliance requirement...'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec 2025 clarification para 3(a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance is filed by email to SEBI, an exchange or a depository</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article; guide Ch.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submission mechanism and formats prescribed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/131 Part B; Dec 2025 Annexure A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The circulars prescribe no penalty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issued under s.11(1); no penalty clause in any circular read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All five read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor claims of a penalty regime describe SEBI's general powers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Six circulars'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRECTED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI's own Dec clarification references three prior circulars; the May 2025 KYC circular is a different series (MIRSD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec 2025 clarification reference table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrected to: five digital accessibility circulars, preceded by a KYC circular.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Nothing in six circulars requires publication'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One of the six has not been read against primary text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrowed to the five actually read.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 obligations: 7 public, 4 artifact, 2 client, 11 not observable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article; repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own classification, published in full</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation/obligations.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presented as a classification, not a finding of fact. 7+4+2+11=24.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI's own Investor Charter contains no digital accessibility right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64,777 chars retrieved; zero matches for 'digital accessib' or 'disabilit'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">investor.sebi.gov.in/Investor-charter.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The most recent Investor Charter circular for stock brokers is 21 Feb 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circular located; Dec 2025 to May 2026 window not exhaustively searched</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI/HO/MIRSD/MIRSD-PoD1/P/CIR/2025/22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep the hedge 'that I can locate'. Tracked as OQ-1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Eleven brokers' charters'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten. 5paisa returns HTTP 403 and no charter was retrievable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">out/charter-verification.json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrected throughout the article.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None of the charters checked contains the digital accessibility right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 documents, 10 brokers, ~414,000 chars, whitespace-normalised. Zero matches</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Every charter is the standard SEBI template, word for word'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only 7 of 10 carry the legacy clause XVII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Removed; replaced with the claim actually evidenced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corpus adequacy for two brokers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotak 2,728 chars and HDFC 5,874 are thin; likely landing pages not full charters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stated as a caveat in the article.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Angel One's charter neither 'accessib' nor 'disab' appears</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34,416 chars, neither string present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">out/charters/angel-one.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Of the brokers checked, one publishes an accessibility statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article; guide Ch.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disclosure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotak Securities; page retrieved and read in full</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kotakneo.com/disclaimer/web-accessibility-statement/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotak's statement names Pivotal Accessibility, 'a DEPwD empaneled auditor'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbatim from the live page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kotakneo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotak names no conformance standard or level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbatim: 'recognised accessibility standards'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Kotak's statement is thin'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It declares scope, names an auditor, states a phased roadmap, carries a Known Limitations section and a feedback route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ungenerous. Article rewritten to credit it before noting gaps.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI s.5.1 specifies IAAP; Pivotal is described as DEPwD-empanelled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both verbatim from their sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111 s.5.1; kotakneo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame as a discrepancy, not as Pivotal being unqualified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UTI AMC says it is 'progressively working towards enhancing digital accessibility in line with the WCAG'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbatim from the filed BRSR PDF, which carries independent assurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UTI/AMC/CS/SE/2026-27/0682, 24 Jun 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About a third of investor PDFs are untagged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 of 76 PDFs hosted on the brokers' own domains lack a structure tree = 32.9%. Including third-party hosts it is 31 of 84 = 36.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">out/pdfcheck.json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The article says 'from the brokers' own websites', so the 25/76 basis is the correct one. State the basis whenever the figure is used.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'SEBI's own circular PDFs are tagged'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three checked, all pass. Cannot generalise to all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/111, 2025/131, Dec 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article says 'the three I checked'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendors cite WCAG 2.1/2.2 AA, GIGW 3.0, IS 17802:2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Third party</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BarrierBreak readiness guide; enabled.in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'A seven-thousand-word readiness document'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approximately 12,000-13,000 words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrected.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Still lists 31 July 2026, three weeks after it moved'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The page shows no publication or revision date at all, so no claim about when it was updated is available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrected to 'as retrieved on 20 August 2026, it lists...'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">That guide lists the cancelled 14 Dec 2025 milestone as live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both sections confirmed on the live page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enabled.in advertises 'IAAP Certified' as a corporate credential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page text confirmed; IAAP certifies individuals, not companies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enabled.in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame as a precision point, not an accusation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Kotak has the lowest critical-violation density'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chat, 20 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OVERSTATED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALSE. Four brokers sit at 0.00/1k; Kotak is fifth at 0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broker Data tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdrawn. Never published.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Kotak has no failing charter PDFs'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISLEADING. Kotak had zero charter PDFs tested; 0/0 is not a pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same for Zerodha, HDFC and Dhan. Withdrawn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotak has the lowest serious-violation density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21 per 1,000 DOM nodes, lowest of ten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subject to S1 - unverified by hand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotak is the only broker with a published accessibility statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chat; article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link enumeration across ten home pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Kotak is best at nearly everything'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two of the four supporting claims fail. What survives is K3 and K4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdrawn. Do not build a piece on it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Disclosure does not predict artifact quality'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNVERIFIED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spearman rho = 0.30, weakly positive. Band A has near-zero variance (7 of 10 score nil) so the correlation is not interpretable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypothesis not supported. Not publishable either way at n=10.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Band A cannot carry a scored article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range is 0/6 to 1/6; seven of ten score zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Band B has a fortyfold spread in serious-violation density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21 (Kotak) to 89.69 (Zerodha) per 1,000 DOM nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This workbook's own first build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three errors found on review: it carried the un-normalised legacy-clause count (6, should be 7); it computed the untagged-PDF share on the wrong basis; and it counted 5paisa's unmeasured Band A as a zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">self-review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The last is the exact error the rubric forbids -- scoring an unmeasured item as a failure. 5paisa now shows 'not measured'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All axe, reflow, text-spacing and focus-visibility results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not published</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No manual reproduction pass has been run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">out/scan.json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GATE: nothing from the scan may be published until each failure is reproduced by hand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUMMARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total claims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrower than first stated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overstated / withdrawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not yet verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Failed verification (corrected + overstated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every 'Source' entry is a document retrieved and read in full, not a summary of it. Verified 20 August 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Band A score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Band A max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surfaces scanned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critical /1k DOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serious /1k DOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total violation nodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worst surface</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charter PDFs tested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charter PDFs failing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All PDFs tested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDFs untagged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accessibility statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Groww</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">account_opening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zerodha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angel One</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grievance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICICI Securities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">investor_charter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotak Securities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDFC Securities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBI Securities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dhan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motilal Oswal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5paisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not measured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTALS / RANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brokers in sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brokers actually measured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">With a published statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Band A scoring zero (of those measured)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brokers at zero critical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowest serious /1k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highest serious /1k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All PDFs untagged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WARNING: every Band B figure (columns G-I) is UNVERIFIED BY HAND -- see claim S1. Nothing here is publishable until each failure is manually reproduced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan run 2026-08-20T02:50:13.406Z. 5paisa excluded from Band B: returns HTTP 403 to automated agents. No workaround attempted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Charter PDFs tested = 0' means none were found, NOT that none failed. Zerodha, Kotak, HDFC and Dhan are 0/0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5paisa is shown as 'not measured', never as zero. Scoring an unmeasured item as a failure is the error this project's rubric forbids.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Untagged-PDF share: 25 of 76 (32.9%) counting only PDFs on the brokers' own domains; 31 of 84 (36.9%) including third-party hosts. State the basis whenever quoting it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documents retrieved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Characters of text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contains 'digital accessibility'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy clause XVII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any 'accessib'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any 'disab'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corpus adequacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conclusive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thin - weak evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT RETRIEVED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Characters of charter text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrying the digital accessibility right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrying legacy clause XVII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conclusive corpora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Method: each broker's charter page plus every charter-shaped PDF linked from it. Text whitespace-normalised before matching -- pdftotext line-wrapping broke a multi-word regex on the first run and undercounted clause XVII by one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circular number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI/HO/MIRSD/SECFATF/P/CIR/2025/74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 May 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accessible digital KYC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT YET READ against primary text (OQ-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsdl.co.in mirror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI/HO/ITD-1/ITD_VIAP/P/CIR/2025/111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 Jul 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base circular; Annexure I carries the substance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read in full</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apmiindia.org mirror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI/HO/ITD-1/ITD_VIAP/P/CIR/2025/121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 Aug 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extended all timelines; IA/RA reporting moved to BSE Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUFG Intime mirror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBI/HO/ITD-1/ITD_VIAP/P/CIR/2025/131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 Sep 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance guidelines, Tables A-D, submission formats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HO/13/19/13(2)2025-ITD-1_VIAP/I/187/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08 Dec 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Replaced auditor milestone; Investor Charter right; SCORES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HO/(411)2026-ITD-5_DIV2/I/17922/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 Jul 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audit and remediation extended to 31 Oct 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read via reproducing notice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSE Notice 20260731-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sebi.gov.in is reachable with an explicit DNS resolve; the local resolver returns NXDOMAIN:  curl --resolve www.sebi.gov.in:443:202.191.181.158 https://www.sebi.gov.in/...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mirrors are the exact SEBI PDFs redistributed by regulated market bodies under SEBI's supervision, not vendor summaries.</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>Where it appears</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Evidence</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Correction / note</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>Supreme Court, 30 Apr 2025, held the right to digital access an intrinsic component of the right to life and personal liberty</t>
+  </si>
+  <si>
+    <t>Article; guide Ch.3</t>
+  </si>
+  <si>
+    <t>Regulation</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>Quoted verbatim inside the circular itself</t>
+  </si>
+  <si>
+    <t>SEBI 2025/111 Annexure I s.A</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>The case is Pragya Prasun &amp; Ors. v. Union of India, heard with a Jain matter</t>
+  </si>
+  <si>
+    <t>Article; guide</t>
+  </si>
+  <si>
+    <t>NARROWER</t>
+  </si>
+  <si>
+    <t>Circular names 'Pragya Prasun &amp; Ors.' and 'Jain vs. Union of India'</t>
+  </si>
+  <si>
+    <t>First name 'Amar' comes from secondary coverage only. Article corrected to 'a Jain matter'.</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>Standards are WCAG 2.1 or latest, GIGW latest, IS 17802, RPwD Act</t>
+  </si>
+  <si>
+    <t>Article; guide Ch.4</t>
+  </si>
+  <si>
+    <t>Verbatim, four numbered items</t>
+  </si>
+  <si>
+    <t>SEBI 2025/111 Annexure I s.B</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>SEBI never writes WCAG 2.2, GIGW 3.0, or a year for IS 17802</t>
+  </si>
+  <si>
+    <t>Article</t>
+  </si>
+  <si>
+    <t>Full text of four circulars searched</t>
+  </si>
+  <si>
+    <t>2025/111, 2025/121, 2025/131, Dec 2025</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>A Nodal Officer for digital accessibility is mandatory</t>
+  </si>
+  <si>
+    <t>Verbatim</t>
+  </si>
+  <si>
+    <t>2025/111 s.1.1-1.2</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>An accessibility-specific grievance mechanism with escalation is required</t>
+  </si>
+  <si>
+    <t>2025/111 s.1.3</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>Investor PDFs must follow accessible document standards; circular cites the WCAG PDF techniques</t>
+  </si>
+  <si>
+    <t>Verbatim, with the W3C URL</t>
+  </si>
+  <si>
+    <t>2025/111 s.2.2</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>ISL, captions, descriptive audio and alt text are required</t>
+  </si>
+  <si>
+    <t>2025/111 s.2.1</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>Audits must include usability testing by persons with disabilities</t>
+  </si>
+  <si>
+    <t>2025/111 s.5.1</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>A disabled applicant may be rejected only after human review, with power to override automation</t>
+  </si>
+  <si>
+    <t>2025/111 s.4.2</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>Responsibility for platform accessibility stays with the RE even for SaaS</t>
+  </si>
+  <si>
+    <t>The circular says 'responsibility', not 'liability'</t>
+  </si>
+  <si>
+    <t>2025/111 s.6.1</t>
+  </si>
+  <si>
+    <t>Article corrected: 'liability' replaced in two places.</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>Audit and remediation deadline is 31 October 2026</t>
+  </si>
+  <si>
+    <t>Circular reproduced inside an exchange notice</t>
+  </si>
+  <si>
+    <t>HO/(411)2026-ITD-5_DIV2/I/17922/2026 via BSE Notice 20260731-17</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>The 14 Dec 2025 auditor milestone was replaced, not supplemented</t>
+  </si>
+  <si>
+    <t>Verbatim: 'Instead of meeting the compliance requirement...'</t>
+  </si>
+  <si>
+    <t>Dec 2025 clarification para 3(a)</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>Compliance is filed by email to SEBI, an exchange or a depository</t>
+  </si>
+  <si>
+    <t>Article; guide Ch.5</t>
+  </si>
+  <si>
+    <t>Submission mechanism and formats prescribed</t>
+  </si>
+  <si>
+    <t>2025/131 Part B; Dec 2025 Annexure A</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>The circulars prescribe no penalty</t>
+  </si>
+  <si>
+    <t>Issued under s.11(1); no penalty clause in any circular read</t>
+  </si>
+  <si>
+    <t>All five read</t>
+  </si>
+  <si>
+    <t>Vendor claims of a penalty regime describe SEBI's general powers.</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>'Six circulars'</t>
+  </si>
+  <si>
+    <t>Article v1</t>
+  </si>
+  <si>
+    <t>CORRECTED</t>
+  </si>
+  <si>
+    <t>SEBI's own Dec clarification references three prior circulars; the May 2025 KYC circular is a different series (MIRSD)</t>
+  </si>
+  <si>
+    <t>Dec 2025 clarification reference table</t>
+  </si>
+  <si>
+    <t>Corrected to: five digital accessibility circulars, preceded by a KYC circular.</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>'Nothing in six circulars requires publication'</t>
+  </si>
+  <si>
+    <t>One of the six has not been read against primary text</t>
+  </si>
+  <si>
+    <t>OQ-3</t>
+  </si>
+  <si>
+    <t>Narrowed to the five actually read.</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>24 obligations: 7 public, 4 artifact, 2 client, 11 not observable</t>
+  </si>
+  <si>
+    <t>Article; repo</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Own classification, published in full</t>
+  </si>
+  <si>
+    <t>regulation/obligations.md</t>
+  </si>
+  <si>
+    <t>Presented as a classification, not a finding of fact. 7+4+2+11=24.</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>SEBI's own Investor Charter contains no digital accessibility right</t>
+  </si>
+  <si>
+    <t>Charter</t>
+  </si>
+  <si>
+    <t>64,777 chars retrieved; zero matches for 'digital accessib' or 'disabilit'</t>
+  </si>
+  <si>
+    <t>investor.sebi.gov.in/Investor-charter.html</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>The most recent Investor Charter circular for stock brokers is 21 Feb 2025</t>
+  </si>
+  <si>
+    <t>Circular located; Dec 2025 to May 2026 window not exhaustively searched</t>
+  </si>
+  <si>
+    <t>SEBI/HO/MIRSD/MIRSD-PoD1/P/CIR/2025/22</t>
+  </si>
+  <si>
+    <t>Keep the hedge 'that I can locate'. Tracked as OQ-1.</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>'Eleven brokers' charters'</t>
+  </si>
+  <si>
+    <t>Ten. 5paisa returns HTTP 403 and no charter was retrievable</t>
+  </si>
+  <si>
+    <t>out/charter-verification.json</t>
+  </si>
+  <si>
+    <t>Corrected throughout the article.</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>None of the charters checked contains the digital accessibility right</t>
+  </si>
+  <si>
+    <t>32 documents, 10 brokers, ~414,000 chars, whitespace-normalised. Zero matches</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>'Every charter is the standard SEBI template, word for word'</t>
+  </si>
+  <si>
+    <t>Only 7 of 10 carry the legacy clause XVII</t>
+  </si>
+  <si>
+    <t>Removed; replaced with the claim actually evidenced.</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>Corpus adequacy for two brokers</t>
+  </si>
+  <si>
+    <t>Kotak 2,728 chars and HDFC 5,874 are thin; likely landing pages not full charters</t>
+  </si>
+  <si>
+    <t>Stated as a caveat in the article.</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>In Angel One's charter neither 'accessib' nor 'disab' appears</t>
+  </si>
+  <si>
+    <t>34,416 chars, neither string present</t>
+  </si>
+  <si>
+    <t>out/charters/angel-one.txt</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Of the brokers checked, one publishes an accessibility statement</t>
+  </si>
+  <si>
+    <t>Article; guide Ch.6</t>
+  </si>
+  <si>
+    <t>Disclosure</t>
+  </si>
+  <si>
+    <t>Kotak Securities; page retrieved and read in full</t>
+  </si>
+  <si>
+    <t>kotakneo.com/disclaimer/web-accessibility-statement/</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Kotak's statement names Pivotal Accessibility, 'a DEPwD empaneled auditor'</t>
+  </si>
+  <si>
+    <t>Verbatim from the live page</t>
+  </si>
+  <si>
+    <t>kotakneo.com</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Kotak names no conformance standard or level</t>
+  </si>
+  <si>
+    <t>Verbatim: 'recognised accessibility standards'</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>'Kotak's statement is thin'</t>
+  </si>
+  <si>
+    <t>It declares scope, names an auditor, states a phased roadmap, carries a Known Limitations section and a feedback route</t>
+  </si>
+  <si>
+    <t>Ungenerous. Article rewritten to credit it before noting gaps.</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>SEBI s.5.1 specifies IAAP; Pivotal is described as DEPwD-empanelled</t>
+  </si>
+  <si>
+    <t>Both verbatim from their sources</t>
+  </si>
+  <si>
+    <t>2025/111 s.5.1; kotakneo.com</t>
+  </si>
+  <si>
+    <t>Frame as a discrepancy, not as Pivotal being unqualified.</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>UTI AMC says it is 'progressively working towards enhancing digital accessibility in line with the WCAG'</t>
+  </si>
+  <si>
+    <t>Verbatim from the filed BRSR PDF, which carries independent assurance</t>
+  </si>
+  <si>
+    <t>UTI/AMC/CS/SE/2026-27/0682, 24 Jun 2026</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>About a third of investor PDFs are untagged</t>
+  </si>
+  <si>
+    <t>25 of 76 PDFs hosted on the brokers' own domains lack a structure tree = 32.9%. Including third-party hosts it is 31 of 84 = 36.9%</t>
+  </si>
+  <si>
+    <t>out/pdfcheck.json</t>
+  </si>
+  <si>
+    <t>The article says 'from the brokers' own websites', so the 25/76 basis is the correct one. State the basis whenever the figure is used.</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>'SEBI's own circular PDFs are tagged'</t>
+  </si>
+  <si>
+    <t>Three checked, all pass. Cannot generalise to all</t>
+  </si>
+  <si>
+    <t>2025/111, 2025/131, Dec 2025</t>
+  </si>
+  <si>
+    <t>Article says 'the three I checked'.</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Vendors cite WCAG 2.1/2.2 AA, GIGW 3.0, IS 17802:2021</t>
+  </si>
+  <si>
+    <t>Third party</t>
+  </si>
+  <si>
+    <t>BarrierBreak readiness guide; enabled.in</t>
+  </si>
+  <si>
+    <t>Live pages</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>'A seven-thousand-word readiness document'</t>
+  </si>
+  <si>
+    <t>Approximately 12,000-13,000 words</t>
+  </si>
+  <si>
+    <t>Live page</t>
+  </si>
+  <si>
+    <t>Corrected.</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>'Still lists 31 July 2026, three weeks after it moved'</t>
+  </si>
+  <si>
+    <t>The page shows no publication or revision date at all, so no claim about when it was updated is available</t>
+  </si>
+  <si>
+    <t>Corrected to 'as retrieved on 20 August 2026, it lists...'</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>That guide lists the cancelled 14 Dec 2025 milestone as live</t>
+  </si>
+  <si>
+    <t>Both sections confirmed on the live page</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>enabled.in advertises 'IAAP Certified' as a corporate credential</t>
+  </si>
+  <si>
+    <t>Page text confirmed; IAAP certifies individuals, not companies</t>
+  </si>
+  <si>
+    <t>enabled.in</t>
+  </si>
+  <si>
+    <t>Frame as a precision point, not an accusation.</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>'Kotak has the lowest critical-violation density'</t>
+  </si>
+  <si>
+    <t>Chat, 20 Aug</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>OVERSTATED</t>
+  </si>
+  <si>
+    <t>FALSE. Four brokers sit at 0.00/1k; Kotak is fifth at 0.21</t>
+  </si>
+  <si>
+    <t>Broker Data tab</t>
+  </si>
+  <si>
+    <t>Withdrawn. Never published.</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>'Kotak has no failing charter PDFs'</t>
+  </si>
+  <si>
+    <t>MISLEADING. Kotak had zero charter PDFs tested; 0/0 is not a pass</t>
+  </si>
+  <si>
+    <t>Same for Zerodha, HDFC and Dhan. Withdrawn.</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>Kotak has the lowest serious-violation density</t>
+  </si>
+  <si>
+    <t>2.21 per 1,000 DOM nodes, lowest of ten</t>
+  </si>
+  <si>
+    <t>Subject to S1 - unverified by hand.</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>Kotak is the only broker with a published accessibility statement</t>
+  </si>
+  <si>
+    <t>Chat; article</t>
+  </si>
+  <si>
+    <t>Link enumeration across ten home pages</t>
+  </si>
+  <si>
+    <t>K5</t>
+  </si>
+  <si>
+    <t>'Kotak is best at nearly everything'</t>
+  </si>
+  <si>
+    <t>Two of the four supporting claims fail. What survives is K3 and K4</t>
+  </si>
+  <si>
+    <t>Withdrawn. Do not build a piece on it.</t>
+  </si>
+  <si>
+    <t>K6</t>
+  </si>
+  <si>
+    <t>'Disclosure does not predict artifact quality'</t>
+  </si>
+  <si>
+    <t>UNVERIFIED</t>
+  </si>
+  <si>
+    <t>Spearman rho = 0.30, weakly positive. Band A has near-zero variance (7 of 10 score nil) so the correlation is not interpretable</t>
+  </si>
+  <si>
+    <t>Hypothesis not supported. Not publishable either way at n=10.</t>
+  </si>
+  <si>
+    <t>K7</t>
+  </si>
+  <si>
+    <t>Band A cannot carry a scored article</t>
+  </si>
+  <si>
+    <t>Range is 0/6 to 1/6; seven of ten score zero</t>
+  </si>
+  <si>
+    <t>K8</t>
+  </si>
+  <si>
+    <t>Band B has a fortyfold spread in serious-violation density</t>
+  </si>
+  <si>
+    <t>2.21 (Kotak) to 89.69 (Zerodha) per 1,000 DOM nodes</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>This workbook's own first build</t>
+  </si>
+  <si>
+    <t>Workbook</t>
+  </si>
+  <si>
+    <t>Three errors found on review: it carried the un-normalised legacy-clause count (6, should be 7); it computed the untagged-PDF share on the wrong basis; and it counted 5paisa's unmeasured Band A as a zero</t>
+  </si>
+  <si>
+    <t>self-review</t>
+  </si>
+  <si>
+    <t>The last is the exact error the rubric forbids -- scoring an unmeasured item as a failure. 5paisa now shows 'not measured'.</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>All axe, reflow, text-spacing and focus-visibility results</t>
+  </si>
+  <si>
+    <t>Not published</t>
+  </si>
+  <si>
+    <t>Scan</t>
+  </si>
+  <si>
+    <t>No manual reproduction pass has been run</t>
+  </si>
+  <si>
+    <t>out/scan.json</t>
+  </si>
+  <si>
+    <t>GATE: nothing from the scan may be published until each failure is reproduced by hand.</t>
+  </si>
+  <si>
+    <t>SUMMARY</t>
+  </si>
+  <si>
+    <t>Total claims</t>
+  </si>
+  <si>
+    <t>Narrower than first stated</t>
+  </si>
+  <si>
+    <t>Corrected</t>
+  </si>
+  <si>
+    <t>Overstated / withdrawn</t>
+  </si>
+  <si>
+    <t>Not yet verified</t>
+  </si>
+  <si>
+    <t>Failed verification (corrected + overstated)</t>
+  </si>
+  <si>
+    <t>Every 'Source' entry is a document retrieved and read in full, not a summary of it. Verified 20 August 2026.</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Broker</t>
+  </si>
+  <si>
+    <t>Band A score</t>
+  </si>
+  <si>
+    <t>Band A max</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Surfaces scanned</t>
+  </si>
+  <si>
+    <t>Critical /1k DOM</t>
+  </si>
+  <si>
+    <t>Serious /1k DOM</t>
+  </si>
+  <si>
+    <t>Total violation nodes</t>
+  </si>
+  <si>
+    <t>Worst surface</t>
+  </si>
+  <si>
+    <t>Charter PDFs tested</t>
+  </si>
+  <si>
+    <t>Charter PDFs failing</t>
+  </si>
+  <si>
+    <t>All PDFs tested</t>
+  </si>
+  <si>
+    <t>PDFs untagged</t>
+  </si>
+  <si>
+    <t>Accessibility statement</t>
+  </si>
+  <si>
+    <t>Groww</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>account_opening</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Zerodha</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>Angel One</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>grievance</t>
+  </si>
+  <si>
+    <t>ICICI Securities</t>
+  </si>
+  <si>
+    <t>investor_charter</t>
+  </si>
+  <si>
+    <t>Upstox</t>
+  </si>
+  <si>
+    <t>Kotak Securities</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>HDFC Securities</t>
+  </si>
+  <si>
+    <t>SBI Securities</t>
+  </si>
+  <si>
+    <t>Dhan</t>
+  </si>
+  <si>
+    <t>Motilal Oswal</t>
+  </si>
+  <si>
+    <t>5paisa</t>
+  </si>
+  <si>
+    <t>not measured</t>
+  </si>
+  <si>
+    <t>TOTALS / RANGE</t>
+  </si>
+  <si>
+    <t>Brokers in sample</t>
+  </si>
+  <si>
+    <t>Brokers actually measured</t>
+  </si>
+  <si>
+    <t>With a published statement</t>
+  </si>
+  <si>
+    <t>Band A scoring zero (of those measured)</t>
+  </si>
+  <si>
+    <t>Brokers at zero critical</t>
+  </si>
+  <si>
+    <t>Lowest serious /1k</t>
+  </si>
+  <si>
+    <t>Highest serious /1k</t>
+  </si>
+  <si>
+    <t>All PDFs untagged</t>
+  </si>
+  <si>
+    <t>WARNING: every Band B figure (columns G-I) is UNVERIFIED BY HAND -- see claim S1. Nothing here is publishable until each failure is manually reproduced.</t>
+  </si>
+  <si>
+    <t>Scan run 2026-08-20T02:50:13.406Z. 5paisa excluded from Band B: returns HTTP 403 to automated agents. No workaround attempted.</t>
+  </si>
+  <si>
+    <t>'Charter PDFs tested = 0' means none were found, NOT that none failed. Zerodha, Kotak, HDFC and Dhan are 0/0.</t>
+  </si>
+  <si>
+    <t>5paisa is shown as 'not measured', never as zero. Scoring an unmeasured item as a failure is the error this project's rubric forbids.</t>
+  </si>
+  <si>
+    <t>Untagged-PDF share: 25 of 76 (32.9%) counting only PDFs on the brokers' own domains; 31 of 84 (36.9%) including third-party hosts. State the basis whenever quoting it.</t>
+  </si>
+  <si>
+    <t>Documents retrieved</t>
+  </si>
+  <si>
+    <t>Characters of text</t>
+  </si>
+  <si>
+    <t>Contains 'digital accessibility'</t>
+  </si>
+  <si>
+    <t>Legacy clause XVII</t>
+  </si>
+  <si>
+    <t>Any 'accessib'</t>
+  </si>
+  <si>
+    <t>Any 'disab'</t>
+  </si>
+  <si>
+    <t>Corpus adequacy</t>
+  </si>
+  <si>
+    <t>conclusive</t>
+  </si>
+  <si>
+    <t>thin - weak evidence</t>
+  </si>
+  <si>
+    <t>NOT RETRIEVED</t>
+  </si>
+  <si>
+    <t>Characters of charter text</t>
+  </si>
+  <si>
+    <t>Carrying the digital accessibility right</t>
+  </si>
+  <si>
+    <t>Carrying legacy clause XVII</t>
+  </si>
+  <si>
+    <t>Conclusive corpora</t>
+  </si>
+  <si>
+    <t>Method: each broker's charter page plus every charter-shaped PDF linked from it. Text whitespace-normalised before matching -- pdftotext line-wrapping broke a multi-word regex on the first run and undercounted clause XVII by one.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Circular number</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Verification status</t>
+  </si>
+  <si>
+    <t>Source used</t>
+  </si>
+  <si>
+    <t>SEBI/HO/MIRSD/SECFATF/P/CIR/2025/74</t>
+  </si>
+  <si>
+    <t>23 May 2025</t>
+  </si>
+  <si>
+    <t>Accessible digital KYC</t>
+  </si>
+  <si>
+    <t>NOT YET READ against primary text (OQ-3)</t>
+  </si>
+  <si>
+    <t>nsdl.co.in mirror</t>
+  </si>
+  <si>
+    <t>SEBI/HO/ITD-1/ITD_VIAP/P/CIR/2025/111</t>
+  </si>
+  <si>
+    <t>31 Jul 2025</t>
+  </si>
+  <si>
+    <t>Base circular; Annexure I carries the substance</t>
+  </si>
+  <si>
+    <t>Read in full</t>
+  </si>
+  <si>
+    <t>apmiindia.org mirror</t>
+  </si>
+  <si>
+    <t>SEBI/HO/ITD-1/ITD_VIAP/P/CIR/2025/121</t>
+  </si>
+  <si>
+    <t>29 Aug 2025</t>
+  </si>
+  <si>
+    <t>Extended all timelines; IA/RA reporting moved to BSE Ltd</t>
+  </si>
+  <si>
+    <t>MUFG Intime mirror</t>
+  </si>
+  <si>
+    <t>SEBI/HO/ITD-1/ITD_VIAP/P/CIR/2025/131</t>
+  </si>
+  <si>
+    <t>25 Sep 2025</t>
+  </si>
+  <si>
+    <t>Compliance guidelines, Tables A-D, submission formats</t>
+  </si>
+  <si>
+    <t>HO/13/19/13(2)2025-ITD-1_VIAP/I/187/2025</t>
+  </si>
+  <si>
+    <t>08 Dec 2025</t>
+  </si>
+  <si>
+    <t>Replaced auditor milestone; Investor Charter right; SCORES</t>
+  </si>
+  <si>
+    <t>HO/(411)2026-ITD-5_DIV2/I/17922/2026</t>
+  </si>
+  <si>
+    <t>31 Jul 2026</t>
+  </si>
+  <si>
+    <t>Audit and remediation extended to 31 Oct 2026</t>
+  </si>
+  <si>
+    <t>Read via reproducing notice</t>
+  </si>
+  <si>
+    <t>BSE Notice 20260731-17</t>
+  </si>
+  <si>
+    <t>sebi.gov.in is reachable with an explicit DNS resolve; the local resolver returns NXDOMAIN:  curl --resolve www.sebi.gov.in:443:202.191.181.158 https://www.sebi.gov.in/...</t>
+  </si>
+  <si>
+    <t>Mirrors are the exact SEBI PDFs redistributed by regulated market bodies under SEBI's supervision, not vendor summaries.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1054,53 +1067,38 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <i/>
+      <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1142,14 +1140,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1159,154 +1157,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F3864"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1365,17 +1254,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1417,12 +1318,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1451,7 +1352,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1472,7 +1373,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1523,7 +1424,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1541,33 +1442,32 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I60"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="52"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="52" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1623,7 +1523,7 @@
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -1652,7 +1552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1679,7 +1579,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -1706,7 +1606,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
@@ -1733,7 +1633,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
@@ -1760,7 +1660,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -1787,7 +1687,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>44</v>
       </c>
@@ -1814,7 +1714,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>47</v>
       </c>
@@ -1841,7 +1741,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
@@ -1868,7 +1768,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
@@ -1897,7 +1797,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>58</v>
       </c>
@@ -1924,7 +1824,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
@@ -1951,7 +1851,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>66</v>
       </c>
@@ -1978,7 +1878,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>71</v>
       </c>
@@ -2007,7 +1907,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>76</v>
       </c>
@@ -2036,7 +1936,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -2065,7 +1965,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>88</v>
       </c>
@@ -2094,7 +1994,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>95</v>
       </c>
@@ -2121,7 +2021,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>100</v>
       </c>
@@ -2150,7 +2050,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>105</v>
       </c>
@@ -2179,7 +2079,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>110</v>
       </c>
@@ -2206,7 +2106,7 @@
       </c>
       <c r="I23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>113</v>
       </c>
@@ -2235,7 +2135,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>117</v>
       </c>
@@ -2264,7 +2164,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>121</v>
       </c>
@@ -2291,7 +2191,7 @@
       </c>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>125</v>
       </c>
@@ -2310,7 +2210,7 @@
       <c r="F27" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="12" t="s">
         <v>130</v>
       </c>
       <c r="H27" s="2" t="s">
@@ -2318,7 +2218,7 @@
       </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>131</v>
       </c>
@@ -2345,7 +2245,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>135</v>
       </c>
@@ -2372,7 +2272,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>138</v>
       </c>
@@ -2401,7 +2301,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>142</v>
       </c>
@@ -2430,7 +2330,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>147</v>
       </c>
@@ -2449,7 +2349,7 @@
       <c r="F32" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="12" t="s">
         <v>150</v>
       </c>
       <c r="H32" s="2" t="s">
@@ -2457,7 +2357,7 @@
       </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:9" ht="42" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>151</v>
       </c>
@@ -2486,7 +2386,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>156</v>
       </c>
@@ -2515,7 +2415,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>161</v>
       </c>
@@ -2542,7 +2442,7 @@
       </c>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>166</v>
       </c>
@@ -2571,7 +2471,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>171</v>
       </c>
@@ -2600,7 +2500,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>175</v>
       </c>
@@ -2627,7 +2527,7 @@
       </c>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>178</v>
       </c>
@@ -2656,7 +2556,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>183</v>
       </c>
@@ -2685,7 +2585,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>191</v>
       </c>
@@ -2714,7 +2614,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>195</v>
       </c>
@@ -2743,7 +2643,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>199</v>
       </c>
@@ -2770,7 +2670,7 @@
       </c>
       <c r="I43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>203</v>
       </c>
@@ -2799,7 +2699,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>207</v>
       </c>
@@ -2828,7 +2728,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>212</v>
       </c>
@@ -2855,7 +2755,7 @@
       </c>
       <c r="I46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>215</v>
       </c>
@@ -2884,7 +2784,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>218</v>
       </c>
@@ -2910,7 +2810,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>224</v>
       </c>
@@ -2939,115 +2839,106 @@
         <v>230</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="B52" s="8" t="n">
-        <f aca="false">COUNTA(A2:A49)</f>
+      <c r="B52" s="8">
+        <f>COUNTA(A2:A49)</f>
         <v>48</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="8" t="n">
-        <f aca="false">COUNTIF(E2:E49,"VERIFIED")</f>
+      <c r="B53" s="8">
+        <f>COUNTIF(E2:E49,"VERIFIED")</f>
         <v>30</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B54" s="8" t="n">
-        <f aca="false">COUNTIF(E2:E49,"NARROWER")</f>
+      <c r="B54" s="8">
+        <f>COUNTIF(E2:E49,"NARROWER")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="B55" s="8" t="n">
-        <f aca="false">COUNTIF(E2:E49,"CORRECTED")</f>
+      <c r="B55" s="8">
+        <f>COUNTIF(E2:E49,"CORRECTED")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B56" s="8" t="n">
-        <f aca="false">COUNTIF(E2:E49,"OVERSTATED")</f>
+      <c r="B56" s="8">
+        <f>COUNTIF(E2:E49,"OVERSTATED")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B57" s="8" t="n">
-        <f aca="false">COUNTIF(E2:E49,"UNVERIFIED")</f>
+      <c r="B57" s="8">
+        <f>COUNTIF(E2:E49,"UNVERIFIED")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B58" s="8" t="n">
-        <f aca="false">COUNTIF(E2:E49,"CORRECTED")+COUNTIF(E2:E49,"OVERSTATED")</f>
+      <c r="B58" s="8">
+        <f>COUNTIF(E2:E49,"CORRECTED")+COUNTIF(E2:E49,"OVERSTATED")</f>
         <v>10</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
         <v>238</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I49"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="12" width="12" customWidth="1"/>
+    <col min="13" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>239</v>
       </c>
@@ -3094,478 +2985,478 @@
         <v>253</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>43.44</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="2">
         <v>328</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="2">
         <v>4</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="2">
         <v>1</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="2">
         <v>14</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="2">
         <v>3</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="2">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="2">
         <v>0.52</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="2">
         <v>89.69</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="2">
         <v>231</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="2">
         <v>0</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="2">
         <v>0</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="2">
         <v>0</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="2">
         <v>0</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="2">
         <v>5</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="2">
         <v>1.96</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="2">
         <v>4.08</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="2">
         <v>51</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="2">
         <v>4</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="2">
         <v>0</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="2">
         <v>9</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="2">
         <v>1</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="2">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2">
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="2">
         <v>0.88</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="2">
         <v>77.23</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="2">
         <v>243</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="2">
         <v>4</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="2">
         <v>1</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="2">
         <v>12</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="2">
         <v>6</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="2">
         <v>0</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2">
         <v>0</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="2">
         <v>3.98</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="2">
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="2">
         <v>2</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="2">
         <v>2</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="2">
         <v>11</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="2">
         <v>4</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="2">
         <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="2">
         <v>6</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="2">
         <v>0.21</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="2">
         <v>2.21</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="2">
         <v>44</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="2">
         <v>0</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="2">
         <v>4</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="2">
         <v>2</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="2">
         <v>0</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="2">
         <v>4</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="2">
         <v>1.83</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="2">
         <v>4.79</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="2">
         <v>41</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" s="2">
         <v>0</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" s="2">
         <v>3</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="2">
         <v>3</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="2">
         <v>6</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="2">
         <v>3</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="2">
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>9.62</v>
-      </c>
-      <c r="I9" s="2" t="n">
+      <c r="H9" s="2">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="I9" s="2">
         <v>39</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="2">
         <v>3</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" s="2">
         <v>9</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="2">
         <v>1</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="2">
         <v>0</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>5</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="2">
         <v>5</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="2">
         <v>1.58</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="2">
         <v>29.21</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="2">
         <v>353</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="2">
         <v>0</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" s="2">
         <v>0</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" s="2">
         <v>9</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="2">
         <v>3</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="2">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="2">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="2">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="2">
         <v>12.92</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="2">
         <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="2">
         <v>3</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="L11" s="2">
         <v>3</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="M11" s="2">
         <v>5</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" s="2">
         <v>2</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -3580,7 +3471,7 @@
       <c r="E12" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -3595,182 +3486,174 @@
       <c r="J12" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="2">
         <v>0</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" s="2">
         <v>0</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" s="2">
         <v>0</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="2">
         <v>0</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14" s="8" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <f aca="false">COUNTA(B2:B12)</f>
+      <c r="C15" s="8">
+        <f>COUNTA(B2:B12)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="C16" s="8" t="n">
-        <f aca="false">COUNTA(B2:B12)-COUNTIF(C2:C12,"not measured")</f>
+      <c r="C16" s="8">
+        <f>COUNTA(B2:B12)-COUNTIF(C2:C12,"not measured")</f>
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="C17" s="8" t="n">
-        <f aca="false">COUNTIF(O2:O12,"yes")</f>
+      <c r="C17" s="8">
+        <f>COUNTIF(O2:O12,"yes")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="C18" s="8" t="n">
-        <f aca="false">COUNTIF(C2:C12,0)</f>
+      <c r="C18" s="8">
+        <f>COUNTIF(C2:C12,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="C19" s="8" t="n">
-        <f aca="false">COUNTIF(G2:G12,0)</f>
+      <c r="C19" s="8">
+        <f>COUNTIF(G2:G12,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C20" s="8" t="n">
-        <f aca="false">MIN(H2:H12)</f>
+      <c r="C20" s="8">
+        <f>MIN(H2:H12)</f>
         <v>2.21</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="C21" s="8" t="n">
-        <f aca="false">MAX(H2:H12)</f>
+      <c r="C21" s="8">
+        <f>MAX(H2:H12)</f>
         <v>89.69</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="C22" s="8" t="n">
-        <f aca="false">SUM(L2:L12)</f>
+      <c r="C22" s="8">
+        <f>SUM(L2:L12)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C23" s="8" t="n">
-        <f aca="false">SUM(K2:K12)</f>
+      <c r="C23" s="8">
+        <f>SUM(K2:K12)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="C24" s="8" t="n">
-        <f aca="false">SUM(N2:N12)</f>
+      <c r="C24" s="8">
+        <f>SUM(N2:N12)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="C25" s="8" t="n">
-        <f aca="false">SUM(M2:M12)</f>
+      <c r="C25" s="8">
+        <f>SUM(M2:M12)</f>
         <v>76</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" s="11" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" s="10" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29" s="11" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" s="11" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B31" s="10" t="s">
         <v>287</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>239</v>
       </c>
@@ -3799,17 +3682,17 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>91533</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -3828,17 +3711,17 @@
         <v>295</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>22183</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -3857,17 +3740,17 @@
         <v>295</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>34416</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -3886,17 +3769,17 @@
         <v>295</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="2">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2">
         <v>49058</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -3915,17 +3798,17 @@
         <v>295</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="2">
         <v>3</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>52670</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -3944,17 +3827,17 @@
         <v>295</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="2">
         <v>2728</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -3973,17 +3856,17 @@
         <v>296</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>5874</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -4002,17 +3885,17 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="2">
         <v>43250</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -4031,17 +3914,17 @@
         <v>295</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="2">
         <v>3</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>71436</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -4060,17 +3943,17 @@
         <v>295</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="2">
         <v>4</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="2">
         <v>44057</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -4089,17 +3972,17 @@
         <v>295</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="2">
         <v>0</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -4118,84 +4001,76 @@
         <v>297</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="C14" s="8" t="n">
-        <f aca="false">SUM(C2:C12)</f>
+      <c r="C14" s="8">
+        <f>SUM(C2:C12)</f>
         <v>32</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <f aca="false">SUM(D2:D12)</f>
+      <c r="C15" s="8">
+        <f>SUM(D2:D12)</f>
         <v>417205</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="C16" s="8" t="n">
-        <f aca="false">COUNTIF(E2:E12,"YES")</f>
+      <c r="C16" s="8">
+        <f>COUNTIF(E2:E12,"YES")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C17" s="8" t="n">
-        <f aca="false">COUNTIF(F2:F12,"yes")</f>
+      <c r="C17" s="8">
+        <f>COUNTIF(F2:F12,"yes")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C18" s="8" t="n">
-        <f aca="false">COUNTIF(I2:I12,"conclusive")</f>
+      <c r="C18" s="8">
+        <f>COUNTIF(I2:I12,"conclusive")</f>
         <v>8</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="10" t="s">
         <v>302</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>303</v>
       </c>
@@ -4215,8 +4090,8 @@
         <v>308</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -4235,8 +4110,8 @@
         <v>313</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -4255,8 +4130,8 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -4275,8 +4150,8 @@
         <v>322</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -4295,8 +4170,8 @@
         <v>318</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -4315,8 +4190,8 @@
         <v>318</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -4335,23 +4210,18 @@
         <v>333</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="10" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" s="10" t="s">
         <v>335</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>